--- a/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: I kursen** Friluftsliv vinter** ingår en veckas vistelse i fjällen som är förknippad med kostnader för den studerande.**…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: I kursen **Friluftsliv vinter** ingår en veckas vistelse i fjällen som är förknippad med kostnader för den studerande.**…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: I kursen **Friluftsliv vinter** ingår en veckas vistelse i fjällen som är förknippad med kostnader för den studerande.**…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: I kursen **Friluftsliv vinter** ingår en veckas vistelse i fjällen som är förknippad med kostnader för den studerande. K…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Övrigt" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Övrigt'!$A$1:$E$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Övrigt'!$A$1:$E$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5491,8 +5491,116 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>FHV0001</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisning samt muntliga och skriftliga examinationer sker på engelska, om inte annat meddelas. …</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>FHV0002</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisningen ges på engelska och muntliga och skriftliga examinationer sker på engelska.…</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>FHV0003</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisningen ges på engelska och muntliga och skriftliga examinationer sker på engelska. Kursen …</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>FVV222H</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisning samt muntliga och skriftliga examinationer sker på engelska, om inte annat meddelas.…</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FVV222H</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E187"/>
+  <autoFilter ref="A1:E191"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -5866,6 +5974,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Övrigt" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Övrigt'!$A$1:$E$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Övrigt'!$A$1:$G$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH237</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIH24T</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Tränarprogrammet inriktning hälsa och idrott, 180 hp. Kursen motsvarar IH1133.…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Tränarprogrammet för hälsa och idrott, 180 hp.…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2A6</t>
         </is>
@@ -590,15 +626,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt med Gru…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
@@ -617,15 +663,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med International Powerlifting Federation (IPF). Kursen kan inte ingå i examen vid Högskolan Dala…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
@@ -644,15 +700,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt med Gru…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
@@ -671,15 +737,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt m…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
@@ -698,15 +774,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt med Sty…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
@@ -725,15 +811,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt m…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
@@ -752,15 +848,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt med Bio…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
@@ -779,15 +885,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt m…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
@@ -806,15 +922,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt med Fun…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
@@ -833,15 +959,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftförbundet. Kursen kan inte ingå i examen vid Högskolan Dalarna parallellt m…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
@@ -860,15 +996,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Tränarprogrammet för hälsa och idrott, 180 hp.…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
@@ -887,15 +1033,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2021-02-03</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar IH1137.…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
         </is>
@@ -914,15 +1066,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursplanen ges i samarbete med Svenska Judoförbundet. Kursen motsvarar GIH2LU samt GIH2M6.…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
@@ -941,15 +1099,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftsförbundet. Kursen motsvarar GIH2LT och GIH2M6.…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
@@ -968,15 +1132,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen motsvarar GIH2LW och GIH2M5.…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
@@ -995,15 +1169,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftsförbundet. Kursen motsvarar GIH2LV.…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
@@ -1022,15 +1202,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Judoförbundet. Kursen motsvarar GIH2LY.…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
@@ -1049,15 +1235,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Styrkelyftförbundet. Kursen motsvarar GIH2LX och GIH2M4.…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
@@ -1076,15 +1272,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Klätterförbundet. Kursen motsvarar GIH2LY och GIH2LX.…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
@@ -1103,15 +1305,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Klätterförbundet. Kursen motsvarar GIH2LV och GIH2LW.…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
@@ -1130,15 +1338,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges i samarbete med Svenska Klätterförbundet. Kursen motsvarar GIH2LT och GIH2LU.…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
@@ -1157,15 +1371,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar GIH2DY.…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
@@ -1184,15 +1404,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 hp. Kursen motsvarar GIH2DZ.…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
@@ -1211,15 +1437,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottsränarprogrammet - prestation och hälsa, 180 hp. Kursen motsvarar GIH2E2.…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
@@ -1238,15 +1470,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar GIH2LR.…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
@@ -1265,15 +1503,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 hp. Denna kurs motsvarar kursen IH1132 _Tränarskap 5 …</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
@@ -1292,15 +1536,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 hp. Denna kurs motsvarar kursen GIH24T _Tränarskap 4 …</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
@@ -1319,15 +1569,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar GIH2LQ.…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
@@ -1346,15 +1602,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
@@ -1373,15 +1635,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
         </is>
@@ -1400,15 +1668,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på distans utan fysiska träffar.…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
@@ -1427,15 +1701,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Denna kurs innehåller två fysiska träffar varav den ena är en halvdag utomhus (orientering) och den andra är en tur på t…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
@@ -1454,15 +1734,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 högskolepoäng. Kursen motsvarar IH1139 samt delar av …</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
@@ -1481,15 +1771,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
@@ -1508,15 +1808,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Tränarprogrammet inriktning hälsa och idrott, 180 hp.…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
@@ -1535,15 +1841,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 högskolepoäng. Kursen motsvarar IH1139 samt delar av …</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
@@ -1562,15 +1874,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 högskolepoäng. Kursen motsvarar IH1140 samt delar av …</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
@@ -1589,15 +1907,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 hp. Denna kurs motsvarar kursen IH1132 _Tränarskap 5 …</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
@@ -1616,15 +1940,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Den tidsmässiga ordningen för delkurserna är inte fastställd. Två delkurser kan också ges parallellt under tio veckor om…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
         </is>
@@ -1643,15 +1973,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: I delkurs 2 ingår en veckas obligatorisk fjällvandring som är förknippad med kostnader för den studerande. Ingår i Lärar…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
@@ -1670,15 +2006,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1004.…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
@@ -1697,15 +2039,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1006.…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
@@ -1724,15 +2072,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen vänder sig särskilt till verksamma lärare. Kursen motsvarar ID1010.…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
         </is>
@@ -1751,15 +2105,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1012.…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
@@ -1778,15 +2138,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1003.…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
@@ -1805,15 +2171,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1013.…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
@@ -1832,15 +2204,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1014.…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
@@ -1859,15 +2237,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: För deltagande i kursen krävs viss friluftsutrustning. Friluftsaktiviteterna genomförs under heldagar. Vandringen kommer…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
@@ -1886,15 +2270,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID1009.…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
@@ -1913,15 +2303,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på engelska. Sökande till kursen ska ha kunskaper om utomnordiska idrotts- och friluftsaktiviteter. Genomföra…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
@@ -1940,15 +2336,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges som distanskurs via Internet. Kursen motsvarar PE1043. Kursen ingick i huvudområdet pedagogik till och med 20…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
@@ -1967,15 +2373,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Denna utbildning är en uppdragsutbildning och kan endast sökas av studenter kopplade till Ylab Education. Kursen är nätb…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
         </is>
@@ -1994,15 +2410,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC1016. Kursen ingick i huvudområde medicinsk vetenskap till om med 2013-10-31.…</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
@@ -2021,15 +2447,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC1040. Kursen ingick i huvudområde medicinsk vetenskap till om med 2013-10-31.…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
@@ -2048,15 +2484,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC1015. Kursen ingick i huvudområde medicinsk vetenskap till om med 2013-10-31.…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
@@ -2075,15 +2521,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC1022. Kursen ingick i huvudområde medicinsk vetenskap till om med 2013-10-31.…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
@@ -2102,15 +2558,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2011-03-30</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges på distans och halvfart. Delkurs 1 ,15 hp, ges termin 1 och delkurs 2 och 3 (7,5 hp + 7,5 hp) ges termin 2. S…</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
@@ -2129,15 +2591,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2012-12-05</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>2013-11-25</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Denna utbildning är en uppdragsutbildning och kan endast sökas av studenter kopplade till Ylab School of Health and Exer…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
@@ -2156,15 +2628,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2014-01-23</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MK1034.…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
         </is>
@@ -2183,15 +2665,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
@@ -2210,15 +2698,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
@@ -2237,15 +2731,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
@@ -2264,15 +2764,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
@@ -2291,15 +2797,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
@@ -2318,15 +2830,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
@@ -2345,15 +2863,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
@@ -2372,15 +2896,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges endast som uppdragsutbildning. För att få ut maximal behållning av kursen bör den studerande ha ett uppslag t…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
@@ -2399,15 +2929,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2014-12-09</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar IH1082.…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
@@ -2426,15 +2962,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator eller motsvara…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
@@ -2453,15 +2995,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ges som nätbaserad kurs. För nätbaserad kurs krävs att den studerande har möjlighet att kommunicera med ljud och …</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
@@ -2480,15 +3028,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2016-08-26</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar IH1108.…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
@@ -2507,15 +3061,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Tränarprogrammet, 180 hp. Kursen kan inte tillgodoräknas i examen parallellt med IH1123 på grund av att k…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
@@ -2534,15 +3094,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID2001.…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
@@ -2561,15 +3127,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Varje delkurs kan läsas som fristående kurser. En vecka av kursen genomförs i svenska fjällvärlden. Kursen motsvarar ID2…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
@@ -2588,15 +3160,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: I kursen **Friluftsliv vinter** ingår en veckas vistelse i fjällen som är förknippad med kostnader för den studerande. K…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
@@ -2615,15 +3193,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID2005.…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
@@ -2642,15 +3226,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID2006.…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
@@ -2669,15 +3259,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar ID2002.…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
@@ -2696,15 +3292,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2012-04-11</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter IH3001.…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
         </is>
@@ -2723,15 +3325,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2021-02-17</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar KE0004 Kemi 1.…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
         </is>
@@ -2750,15 +3358,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>2018-10-22</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: För att läsa denna kurs krävs genomgången kurs Personcentrerad vård vid astma/KOL/allergi, del 1. Kursen riktar sig enda…</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
@@ -2777,15 +3395,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår som valbar kurs i Magisterprogram i fysioterapi. Kursen motsvarar MC3023.…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
@@ -2804,15 +3428,25 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC3029.…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
@@ -2831,15 +3465,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
@@ -2858,15 +3502,25 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
@@ -2885,15 +3539,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Magisterprogram i fysioterapi. Kursen överlappar AMC22B.…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
@@ -2912,15 +3572,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>2018-04-16</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Sjuksköterskeprogrammet. Kursen motsvarar MC1073. Kursen genomförs i hög grad med stöd av högskolans digi…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
@@ -2939,15 +3609,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC1076.…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
@@ -2966,15 +3642,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i sjuksköterskeprogrammet. Kursen motsvarar GMC22H.…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
@@ -2993,15 +3679,25 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2013-09-09</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>2014-01-22</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen genomförs i hög grad med stöd av informations- och kommunikationsteknologi vilket förutsätter en fungerande inter…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
@@ -3020,15 +3716,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen genomförs i hög grad med stöd av informations- och kommunikationsteknologi vilket förutsätter en fungerande inter…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
@@ -3047,15 +3749,25 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen genomförs i hög grad med stöd av informations- och kommunikationsteknologi vilket förutsätter en fungerande inter…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
@@ -3074,15 +3786,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter MC2016.…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
@@ -3101,15 +3819,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC2003.…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
         </is>
@@ -3128,15 +3852,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar MC1028.…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
         </is>
@@ -3155,15 +3885,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Förskrivning av vissa läkemedel och förbrukningsartiklar regleras i enlighet med Socialstyrelsens direktiv i SOSFS 2001:…</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
@@ -3182,15 +3918,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen är en uppdragsutbildning som vänder sig till förskollärare, barnskötare och annan pedagogisk personal som är anst…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
@@ -3209,15 +3951,25 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Undervisningsspråk är engelska.…</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
@@ -3236,15 +3988,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Undervisningsspråk är engelska.…</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
@@ -3263,15 +4025,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling. Kursen innehåller tre obliga…</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
@@ -3290,15 +4058,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: För nätbaserad kurs krävs tillgång till dator, headset, webbkamera och internetuppkoppling. Kursen innehåller två obliga…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
@@ -3317,15 +4091,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
@@ -3344,15 +4124,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>2016-03-10</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar PS1013.…</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
         </is>
@@ -3371,15 +4157,25 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
@@ -3398,15 +4194,25 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
         </is>
@@ -3425,15 +4231,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår som valfri kurs i Socionomprogrammet. Kursen motsvarar SA3007.…</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
@@ -3452,15 +4268,25 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen bedrivs nätbaserat. Det krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator ell…</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
@@ -3479,15 +4305,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår som valfri kurs i Socionomprogrammet. Kursen motsvarar VÅ3137 och AVÅ24F. Kursen kan inte ingå i examen vid…</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
@@ -3506,15 +4342,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
         </is>
@@ -3533,15 +4379,25 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SA3010. Kan ingå som kurs i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
         </is>
@@ -3560,15 +4416,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen är en uppdragsutbildning.…</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
@@ -3587,15 +4449,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen bedrivs nätbaserat. Det krävs att den studerande har möjlighet att kommunicera med ljud och bild via en dator ell…</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
         </is>
@@ -3614,15 +4482,25 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>2018-10-19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
@@ -3641,15 +4519,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
@@ -3668,15 +4552,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
         </is>
@@ -3695,15 +4585,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar delkurs 3 i SA2020.…</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
         </is>
@@ -3722,15 +4622,25 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Om en student inte uppnår målen för den verksamhetsförlagda kursen under ordinarie pe…</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -3749,15 +4659,25 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursplanen ingår i Socionomprogrammet. Kursen motsvarar SA1047.…</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
@@ -3776,15 +4696,25 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar GSA27Z.…</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
         </is>
@@ -3803,15 +4733,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar GSA27T.…</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
@@ -3830,15 +4766,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar GSA27U.…</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
@@ -3857,15 +4799,25 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SA1028.…</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
@@ -3884,15 +4836,25 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar/överlappar SO1045.…</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
         </is>
@@ -3911,15 +4873,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar/överlappar GSO23Q. Om en student inte uppnår målen för den verksamhe…</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
@@ -3938,15 +4906,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar/överlappar SO1046 Socialpolitik…</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
@@ -3965,15 +4939,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
@@ -3992,15 +4972,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet.…</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
@@ -4019,15 +5005,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen överlappar GSA24Y.…</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
@@ -4046,15 +5038,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2014-10-14</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SA1004.…</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
@@ -4073,15 +5071,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SA1025.…</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
@@ -4100,15 +5104,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+          <t>2016-05-20</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SA1033.…</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
@@ -4127,15 +5137,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
         </is>
@@ -4154,15 +5170,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar SA1041.…</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
@@ -4181,15 +5203,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Om en student inte uppnår målen för den verksamhetsförlagda kursen/kursmomentet under…</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
@@ -4208,15 +5236,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Socionomprogrammet. Kursen motsvarar SA2019.…</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
@@ -4235,15 +5269,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>2016-09-08</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
         </is>
@@ -4262,15 +5302,21 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
@@ -4289,15 +5335,25 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i magisterprogrammet Global sexuell och reproduktiv hälsa.…</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
@@ -4316,15 +5372,25 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i magisterprogrammet Global sexuell och reproduktiv hälsa.…</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
@@ -4343,15 +5409,25 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i magisterprogrammet Global sexuell och reproduktiv hälsa.…</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
@@ -4370,15 +5446,21 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Barnmorskeprogrammet. Kursen motsvarar delvis SR3010.…</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
@@ -4397,15 +5479,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Barnmorskeprogrammet. Kursen motsvarar delvis SR3010.…</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
@@ -4424,15 +5512,25 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i magisterprogrammet Global sexuell och reproduktiv hälsa.…</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
@@ -4451,15 +5549,25 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i magisterprogrammet Global sexuell och reproduktiv hälsa.…</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
@@ -4478,15 +5586,25 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i magisterprogrammet Global sexuell och reproduktiv hälsa.…</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
@@ -4505,15 +5623,25 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
@@ -4532,15 +5660,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Barnmorskeprogrammet. Kursen motsvarar/överlappar ASR25Q.…</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
@@ -4559,15 +5693,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3106 och SR3011. VFU genomförs enligt schema som Högskolan Dalarna fastställer i samråd med VFU-plats…</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
@@ -4586,15 +5726,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3109 och SR3012. Om en student inte uppnår målen för den verksamhetsförlagda kursen/ kursmomentet und…</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
@@ -4613,15 +5759,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VV3016 och SR3013.…</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
@@ -4640,15 +5792,25 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2021-02-19</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
@@ -4667,15 +5829,25 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursens undervisningsspråk är engelska.…</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
@@ -4694,15 +5866,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3115.…</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
@@ -4721,15 +5899,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3117.…</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
@@ -4748,15 +5932,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3118.…</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
@@ -4775,15 +5965,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3119.…</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
@@ -4802,15 +5998,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3120.…</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
@@ -4829,15 +6031,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3121.…</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
@@ -4856,15 +6064,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3122.…</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
@@ -4883,15 +6097,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen kan enbart läsas av studenter antagna till Barnmorskeprogrammet 90 hp vid Högskolan Dalarna. Kursen motsvarar VÅ3…</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
@@ -4910,15 +6130,25 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen kan enbart läsas av studenter antagna till Barnmorskeprogrammet 90 hp vid Högskolan Dalarna. Kursen motsvarar VÅ3…</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
@@ -4937,15 +6167,25 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3112.…</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
@@ -4964,15 +6204,25 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3106. VFU genomförs enligt schema som Högskolan Dalarna fastställer i samråd med VFU-platsen. Detta k…</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
@@ -4991,15 +6241,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3109. Om en student inte uppnår målen för den verksamhetsförlagda kursen/ kursmomentet under ordinari…</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
@@ -5018,15 +6274,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VV3016.…</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
@@ -5045,15 +6307,25 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3107. VFU genomförs enligt schema som Högskolan Dalarna fastställer i samråd med VFU-platsen. Detta k…</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
@@ -5072,15 +6344,25 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t>2018-01-10</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VÅ3108. Om en student inte uppnår målen för den verksamhetsförlagda kursen/kursmomentet under ordinarie…</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
@@ -5099,15 +6381,25 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
@@ -5126,15 +6418,25 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen motsvarar VV3015.…</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
         </is>
@@ -5153,15 +6455,25 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
+          <t>2009-04-21</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
@@ -5180,15 +6492,25 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>Sektion saknas</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Ingen Övrigt-sektion i kursplanen</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
@@ -5207,15 +6529,21 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Ersätter VV3002 vårterminen 2009.…</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
@@ -5234,15 +6562,25 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2008-03-03</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Motsvarar VV3001.…</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
@@ -5261,15 +6599,25 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Barnmorskeprogrammet. Kursen ersätter VÅ3034 vårterminen 2010. Reviderad 2009-12-03 (vt10), 2010-10-18 (h…</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
@@ -5288,15 +6636,25 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Barnmorskeprogrammet. Kursen ersätter delkurs 1 i VÅ3020 vårterminen 2010. Reviderad 2010-10-18 (ht10).…</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
         </is>
@@ -5315,15 +6673,25 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2009-05-26</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
+          <t>2012-01-26</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Reviderad 2010-11-03 (ht10).…</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
@@ -5342,15 +6710,25 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2009-12-14</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
+          <t>2013-08-26</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter delkurs 2 i VÅ3020. Kursen ingår i barnmorskeprogrammet. Under den verksamhetsförlagda utbildningen på f…</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
@@ -5369,15 +6747,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen ersätter delkurs 1 i VÅ3021. Kursen ingår i Barnmorskeprogrammet. Reviderad 2010-10-18 (ht10).…</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
@@ -5396,15 +6784,25 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
+          <t>2018-11-14</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Institutionen använder sig av plagiatkontroll vilket innebär att examensarbetet kan bli föremål för plagiatkontroll i sa…</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
@@ -5423,15 +6821,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
+          <t>2014-03-06</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen genomförs med stöd av informations- och kommunikationsteknik vilket förutsätter en fungerande internetuppkoppling…</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
@@ -5450,15 +6854,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen genomförs med stöd av informations- och kommunikationsteknik vilket förutsätter en fungerande internetuppkoppling…</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
@@ -5477,15 +6887,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Antal examinationstillfällen är begränsade till fem. Institutionen använder sig av ”Ephorus” plagiatkontroll vilket inne…</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
@@ -5504,15 +6920,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisning samt muntliga och skriftliga examinationer sker på engelska, om inte annat meddelas. …</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
@@ -5531,15 +6953,25 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisningen ges på engelska och muntliga och skriftliga examinationer sker på engelska.…</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
         </is>
@@ -5558,15 +6990,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
         <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisningen ges på engelska och muntliga och skriftliga examinationer sker på engelska. Kursen …</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
         </is>
@@ -5585,403 +7023,413 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Saknar standardfras om pedagogiskt stöd</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
           <t>Saknar standardfras om pedagogiskt stöd: Kursen är nätbaserad. Undervisning samt muntliga och skriftliga examinationer sker på engelska, om inte annat meddelas.…</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FVV222H</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E191"/>
+  <autoFilter ref="A1:G191"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId376"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId380"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Övrigt.xlsx
@@ -1448,7 +1448,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottsränarprogrammet - prestation och hälsa, 180 hp. Kursen motsvarar GIH2E2.…</t>
+          <t>Saknar standardfras om pedagogiskt stöd: Kursen ingår i Idrottstränarprogrammet - prestation och hälsa, 180 hp. Kursen motsvarar GIH2E2.…</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
